--- a/batch/tasks_setting.xlsx
+++ b/batch/tasks_setting.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15488" windowHeight="9317"/>
+    <workbookView windowHeight="15760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="13">
   <si>
     <t>Video File</t>
   </si>
@@ -44,13 +44,28 @@
     <t>Status</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=U4aFbyzrTdc</t>
+    <t>https://www.youtube.com/watch?v=kUpTUEwKnrk</t>
   </si>
   <si>
     <t>en</t>
   </si>
   <si>
-    <t>French</t>
+    <t>简体中文</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=qk5JH6ImK0I</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=TeFCb5-4e5U&amp;t=687s</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=HuTyZiUDz2k</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=85qo6qC4r-0</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KUvSzvFeZls</t>
   </si>
 </sst>
 </file>
@@ -58,12 +73,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -74,13 +89,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -548,156 +556,157 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1044,8 +1053,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="1" outlineLevelCol="4"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
@@ -1065,7 +1074,7 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
@@ -1078,7 +1087,85 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://www.youtube.com/watch?v=kUpTUEwKnrk"/>
+    <hyperlink ref="A3" r:id="rId2" display="https://www.youtube.com/watch?v=qk5JH6ImK0I"/>
+    <hyperlink ref="A4" r:id="rId3" display="https://www.youtube.com/watch?v=TeFCb5-4e5U&amp;t=687s"/>
+    <hyperlink ref="A5" r:id="rId4" display="https://www.youtube.com/watch?v=HuTyZiUDz2k"/>
+    <hyperlink ref="A6" r:id="rId5" display="https://www.youtube.com/watch?v=85qo6qC4r-0"/>
+    <hyperlink ref="A7" r:id="rId6" display="https://www.youtube.com/watch?v=KUvSzvFeZls"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
